--- a/docs/Connect Test Case and Workflow Inventory.xlsx
+++ b/docs/Connect Test Case and Workflow Inventory.xlsx
@@ -6382,7 +6382,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="12.71" customWidth="1" style="86" min="1" max="1"/>
@@ -6471,6 +6471,16 @@
 (Yes / Partial Coverage / No / N/A)</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Tests Automated (Count)</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Not Automatable (Count)</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="59.25" customHeight="1" s="86">
       <c r="A5" s="35" t="n">
@@ -6508,6 +6518,12 @@
         <is>
           <t>N/A - manual, out of scope for Maestro</t>
         </is>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="6" ht="93.75" customHeight="1" s="86">
@@ -6542,6 +6558,12 @@
         <is>
           <t>Partial Coverage (6/7)</t>
         </is>
+      </c>
+      <c r="K6" t="n">
+        <v>6</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7" ht="45.75" customHeight="1" s="86">
@@ -6570,8 +6592,14 @@
       <c r="I7" s="45" t="n"/>
       <c r="J7" s="95" t="inlineStr">
         <is>
-          <t>N/A - already covered by existing on-device script</t>
-        </is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8" ht="87" customHeight="1" s="86">
@@ -6606,6 +6634,12 @@
         <is>
           <t>Partial Coverage (7/14)</t>
         </is>
+      </c>
+      <c r="K8" t="n">
+        <v>7</v>
+      </c>
+      <c r="L8" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="9" ht="45.75" customHeight="1" s="86">
@@ -6637,6 +6671,12 @@
           <t>Partial Coverage (21/22)</t>
         </is>
       </c>
+      <c r="K9" t="n">
+        <v>21</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10" ht="57" customHeight="1" s="86">
       <c r="A10" s="95" t="n">
@@ -6670,6 +6710,12 @@
         <is>
           <t>Partial Coverage (48/66)</t>
         </is>
+      </c>
+      <c r="K10" t="n">
+        <v>48</v>
+      </c>
+      <c r="L10" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="11" ht="45.75" customHeight="1" s="86">
@@ -6698,8 +6744,14 @@
       <c r="I11" s="45" t="n"/>
       <c r="J11" s="95" t="inlineStr">
         <is>
-          <t>N/A - already covered by existing on-device script</t>
-        </is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>2</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12" ht="45.75" customHeight="1" s="86">
@@ -6728,8 +6780,14 @@
       <c r="I12" s="45" t="n"/>
       <c r="J12" s="95" t="inlineStr">
         <is>
-          <t>N/A - already covered by existing on-device script</t>
-        </is>
+          <t>Partial Coverage (4/13)</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>4</v>
+      </c>
+      <c r="L12" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="13" ht="45.75" customHeight="1" s="86">
@@ -6758,8 +6816,14 @@
       <c r="I13" s="45" t="n"/>
       <c r="J13" s="95" t="inlineStr">
         <is>
-          <t>N/A - already covered by existing on-device script</t>
-        </is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>2</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14" ht="45.75" customHeight="1" s="86">
@@ -6788,8 +6852,14 @@
       <c r="I14" s="45" t="n"/>
       <c r="J14" s="95" t="inlineStr">
         <is>
-          <t>N/A - already covered by existing on-device script</t>
-        </is>
+          <t>Partial Coverage (6/8)</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>6</v>
+      </c>
+      <c r="L14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15" ht="39.75" customHeight="1" s="86">
@@ -6821,6 +6891,12 @@
           <t>Partial Coverage (11/13)</t>
         </is>
       </c>
+      <c r="K15" t="n">
+        <v>11</v>
+      </c>
+      <c r="L15" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="16" ht="39.75" customHeight="1" s="86">
       <c r="A16" s="46" t="n">
@@ -6848,8 +6924,14 @@
       <c r="I16" s="67" t="n"/>
       <c r="J16" s="95" t="inlineStr">
         <is>
-          <t>N/A - already covered by existing on-device script</t>
-        </is>
+          <t>Partial Coverage (4/5)</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>4</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17" ht="39.75" customHeight="1" s="86">
@@ -6878,8 +6960,14 @@
       <c r="I17" s="63" t="n"/>
       <c r="J17" s="95" t="inlineStr">
         <is>
-          <t>N/A - already covered by existing on-device script</t>
-        </is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>5</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18" ht="39.75" customHeight="1" s="86">
@@ -6908,8 +6996,14 @@
       <c r="I18" s="67" t="n"/>
       <c r="J18" s="95" t="inlineStr">
         <is>
-          <t>N/A - already covered by existing on-device script</t>
-        </is>
+          <t>Partial Coverage (7/11)</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>7</v>
+      </c>
+      <c r="L18" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="19" ht="49.5" customHeight="1" s="86">
@@ -6944,6 +7038,12 @@
         <is>
           <t>Partial Coverage (7/9)</t>
         </is>
+      </c>
+      <c r="K19" t="n">
+        <v>8</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20" ht="39.75" customHeight="1" s="86">
@@ -6975,6 +7075,12 @@
           <t>Partial Coverage (5/26)</t>
         </is>
       </c>
+      <c r="K20" t="n">
+        <v>5</v>
+      </c>
+      <c r="L20" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="21" ht="39.75" customHeight="1" s="86">
       <c r="A21" s="78" t="n">
@@ -7005,6 +7111,12 @@
           <t>Partial Coverage (23/29)</t>
         </is>
       </c>
+      <c r="K21" t="n">
+        <v>24</v>
+      </c>
+      <c r="L21" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="22" ht="57" customHeight="1" s="86">
       <c r="A22" s="46" t="n">
@@ -7038,6 +7150,12 @@
         <is>
           <t>Partial Coverage (46/47)</t>
         </is>
+      </c>
+      <c r="K22" t="n">
+        <v>46</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23" ht="39.75" customHeight="1" s="86">
@@ -7069,6 +7187,16 @@
           <t>N/A - already covered by existing on-device script</t>
         </is>
       </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>TBD - Form Submissions not yet automated</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="44.25" customHeight="1" s="86">
       <c r="A24" s="46" t="n">
@@ -7102,6 +7230,12 @@
         <is>
           <t>Partial Coverage (1/4)</t>
         </is>
+      </c>
+      <c r="K24" t="n">
+        <v>1</v>
+      </c>
+      <c r="L24" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="25" ht="14.25" customHeight="1" s="86">
@@ -7131,6 +7265,30 @@
       <c r="J25" s="95" t="inlineStr">
         <is>
           <t>Partial Coverage (9/24)</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>9</v>
+      </c>
+      <c r="L25" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>TOTAL (excl. Form Submissions - not yet automated)</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>219</v>
+      </c>
+      <c r="L27" t="n">
+        <v>122</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>63.5% automated (219/345 test cases)</t>
         </is>
       </c>
     </row>

--- a/docs/Connect Test Case and Workflow Inventory.xlsx
+++ b/docs/Connect Test Case and Workflow Inventory.xlsx
@@ -6471,12 +6471,12 @@
 (Yes / Partial Coverage / No / N/A)</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K4" s="0" t="inlineStr">
         <is>
           <t>Tests Automated (Count)</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="L4" s="0" t="inlineStr">
         <is>
           <t>Not Automatable (Count)</t>
         </is>
@@ -6519,10 +6519,10 @@
           <t>N/A - manual, out of scope for Maestro</t>
         </is>
       </c>
-      <c r="K5" t="n">
+      <c r="K5" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L5" s="0" t="n">
         <v>35</v>
       </c>
     </row>
@@ -6559,10 +6559,10 @@
           <t>Partial Coverage (6/7)</t>
         </is>
       </c>
-      <c r="K6" t="n">
+      <c r="K6" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L6" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6595,10 +6595,10 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="K7" t="n">
+      <c r="K7" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L7" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6635,10 +6635,10 @@
           <t>Partial Coverage (7/14)</t>
         </is>
       </c>
-      <c r="K8" t="n">
+      <c r="K8" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="L8" t="n">
+      <c r="L8" s="0" t="n">
         <v>5</v>
       </c>
     </row>
@@ -6671,10 +6671,10 @@
           <t>Partial Coverage (21/22)</t>
         </is>
       </c>
-      <c r="K9" t="n">
+      <c r="K9" s="0" t="n">
         <v>21</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L9" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6711,10 +6711,10 @@
           <t>Partial Coverage (48/66)</t>
         </is>
       </c>
-      <c r="K10" t="n">
+      <c r="K10" s="0" t="n">
         <v>48</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L10" s="0" t="n">
         <v>22</v>
       </c>
     </row>
@@ -6747,10 +6747,10 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="K11" t="n">
+      <c r="K11" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L11" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6783,10 +6783,10 @@
           <t>Partial Coverage (4/13)</t>
         </is>
       </c>
-      <c r="K12" t="n">
+      <c r="K12" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L12" s="0" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6819,10 +6819,10 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="K13" t="n">
+      <c r="K13" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L13" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6855,10 +6855,10 @@
           <t>Partial Coverage (6/8)</t>
         </is>
       </c>
-      <c r="K14" t="n">
+      <c r="K14" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="L14" t="n">
+      <c r="L14" s="0" t="n">
         <v>2</v>
       </c>
     </row>
@@ -6891,10 +6891,10 @@
           <t>Partial Coverage (11/13)</t>
         </is>
       </c>
-      <c r="K15" t="n">
+      <c r="K15" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="L15" t="n">
+      <c r="L15" s="0" t="n">
         <v>2</v>
       </c>
     </row>
@@ -6927,10 +6927,10 @@
           <t>Partial Coverage (4/5)</t>
         </is>
       </c>
-      <c r="K16" t="n">
+      <c r="K16" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="L16" t="n">
+      <c r="L16" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6963,10 +6963,10 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="K17" t="n">
+      <c r="K17" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="L17" t="n">
+      <c r="L17" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6999,10 +6999,10 @@
           <t>Partial Coverage (7/11)</t>
         </is>
       </c>
-      <c r="K18" t="n">
+      <c r="K18" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="L18" t="n">
+      <c r="L18" s="0" t="n">
         <v>4</v>
       </c>
     </row>
@@ -7039,10 +7039,10 @@
           <t>Partial Coverage (7/9)</t>
         </is>
       </c>
-      <c r="K19" t="n">
+      <c r="K19" s="0" t="n">
         <v>8</v>
       </c>
-      <c r="L19" t="n">
+      <c r="L19" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7075,10 +7075,10 @@
           <t>Partial Coverage (5/26)</t>
         </is>
       </c>
-      <c r="K20" t="n">
+      <c r="K20" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="L20" t="n">
+      <c r="L20" s="0" t="n">
         <v>21</v>
       </c>
     </row>
@@ -7111,10 +7111,10 @@
           <t>Partial Coverage (23/29)</t>
         </is>
       </c>
-      <c r="K21" t="n">
+      <c r="K21" s="0" t="n">
         <v>24</v>
       </c>
-      <c r="L21" t="n">
+      <c r="L21" s="0" t="n">
         <v>5</v>
       </c>
     </row>
@@ -7151,10 +7151,10 @@
           <t>Partial Coverage (46/47)</t>
         </is>
       </c>
-      <c r="K22" t="n">
+      <c r="K22" s="0" t="n">
         <v>46</v>
       </c>
-      <c r="L22" t="n">
+      <c r="L22" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7184,18 +7184,14 @@
       <c r="I23" s="63" t="n"/>
       <c r="J23" s="95" t="inlineStr">
         <is>
-          <t>N/A - already covered by existing on-device script</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>TBD - Form Submissions not yet automated</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
+          <t>Partial Coverage (29/51)</t>
+        </is>
+      </c>
+      <c r="K23" s="0" t="n">
+        <v>29</v>
+      </c>
+      <c r="L23" s="0" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="24" ht="44.25" customHeight="1" s="86">
@@ -7231,10 +7227,10 @@
           <t>Partial Coverage (1/4)</t>
         </is>
       </c>
-      <c r="K24" t="n">
+      <c r="K24" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="L24" t="n">
+      <c r="L24" s="0" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7267,28 +7263,28 @@
           <t>Partial Coverage (9/24)</t>
         </is>
       </c>
-      <c r="K25" t="n">
+      <c r="K25" s="0" t="n">
         <v>9</v>
       </c>
-      <c r="L25" t="n">
+      <c r="L25" s="0" t="n">
         <v>15</v>
       </c>
     </row>
     <row r="27">
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>TOTAL (excl. Form Submissions - not yet automated)</t>
-        </is>
-      </c>
-      <c r="K27" t="n">
-        <v>219</v>
-      </c>
-      <c r="L27" t="n">
-        <v>122</v>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>63.5% automated (219/345 test cases)</t>
+      <c r="B27" s="0" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="K27" s="0" t="n">
+        <v>248</v>
+      </c>
+      <c r="L27" s="0" t="n">
+        <v>143</v>
+      </c>
+      <c r="M27" s="0" t="inlineStr">
+        <is>
+          <t>63.4% automated (248/391 test cases)</t>
         </is>
       </c>
     </row>

--- a/docs/Connect Test Case and Workflow Inventory.xlsx
+++ b/docs/Connect Test Case and Workflow Inventory.xlsx
@@ -6668,14 +6668,14 @@
       <c r="I9" s="45" t="n"/>
       <c r="J9" s="95" t="inlineStr">
         <is>
-          <t>Partial Coverage (21/22)</t>
+          <t>Partial Coverage (6/22)</t>
         </is>
       </c>
       <c r="K9" s="0" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="L9" s="0" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" ht="57" customHeight="1" s="86">
@@ -7277,14 +7277,14 @@
         </is>
       </c>
       <c r="K27" s="0" t="n">
-        <v>248</v>
+        <v>233</v>
       </c>
       <c r="L27" s="0" t="n">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="M27" s="0" t="inlineStr">
         <is>
-          <t>63.4% automated (248/391 test cases)</t>
+          <t>59.6% automated (233/391 test cases)</t>
         </is>
       </c>
     </row>

--- a/docs/Connect Test Case and Workflow Inventory.xlsx
+++ b/docs/Connect Test Case and Workflow Inventory.xlsx
@@ -6668,14 +6668,14 @@
       <c r="I9" s="45" t="n"/>
       <c r="J9" s="95" t="inlineStr">
         <is>
-          <t>Partial Coverage (6/22)</t>
+          <t>Partial Coverage (21/22)</t>
         </is>
       </c>
       <c r="K9" s="0" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="L9" s="0" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" ht="57" customHeight="1" s="86">
@@ -6780,11 +6780,11 @@
       <c r="I12" s="45" t="n"/>
       <c r="J12" s="95" t="inlineStr">
         <is>
-          <t>Partial Coverage (4/13)</t>
+          <t>Partial Coverage (8/13)</t>
         </is>
       </c>
       <c r="K12" s="0" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L12" s="0" t="n">
         <v>3</v>
@@ -7036,7 +7036,7 @@
       </c>
       <c r="J19" s="95" t="inlineStr">
         <is>
-          <t>Partial Coverage (7/9)</t>
+          <t>Partial Coverage (8/9)</t>
         </is>
       </c>
       <c r="K19" s="0" t="n">
@@ -7108,11 +7108,11 @@
       <c r="I21" s="63" t="n"/>
       <c r="J21" s="95" t="inlineStr">
         <is>
-          <t>Partial Coverage (23/29)</t>
+          <t>Partial Coverage (23/28)</t>
         </is>
       </c>
       <c r="K21" s="0" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L21" s="0" t="n">
         <v>5</v>
@@ -7148,14 +7148,14 @@
       </c>
       <c r="J22" s="95" t="inlineStr">
         <is>
-          <t>Partial Coverage (46/47)</t>
+          <t>Partial Coverage (44/47)</t>
         </is>
       </c>
       <c r="K22" s="0" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L22" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23" ht="39.75" customHeight="1" s="86">
@@ -7277,14 +7277,14 @@
         </is>
       </c>
       <c r="K27" s="0" t="n">
-        <v>233</v>
+        <v>249</v>
       </c>
       <c r="L27" s="0" t="n">
-        <v>158</v>
+        <v>145</v>
       </c>
       <c r="M27" s="0" t="inlineStr">
         <is>
-          <t>59.6% automated (233/391 test cases)</t>
+          <t>63.2% automated (249/394 test cases)</t>
         </is>
       </c>
     </row>

--- a/docs/Connect Test Case and Workflow Inventory.xlsx
+++ b/docs/Connect Test Case and Workflow Inventory.xlsx
@@ -7108,14 +7108,14 @@
       <c r="I21" s="63" t="n"/>
       <c r="J21" s="95" t="inlineStr">
         <is>
-          <t>Partial Coverage (23/28)</t>
+          <t>Partial Coverage (24/30)</t>
         </is>
       </c>
       <c r="K21" s="0" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L21" s="0" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" ht="57" customHeight="1" s="86">
@@ -7277,14 +7277,14 @@
         </is>
       </c>
       <c r="K27" s="0" t="n">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="L27" s="0" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="M27" s="0" t="inlineStr">
         <is>
-          <t>63.2% automated (249/394 test cases)</t>
+          <t>63.1% automated (250/396 test cases)</t>
         </is>
       </c>
     </row>

--- a/docs/Connect Test Case and Workflow Inventory.xlsx
+++ b/docs/Connect Test Case and Workflow Inventory.xlsx
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="37">
+  <fonts count="38">
     <font>
       <name val="Calibri"/>
       <color theme="1"/>
@@ -232,6 +232,10 @@
       <color theme="1"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="13">
     <fill>
@@ -380,7 +384,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -642,6 +646,12 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -7249,15 +7259,19 @@
           <t>High</t>
         </is>
       </c>
-      <c r="E25" s="82" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="E25" s="96" t="inlineStr">
+        <is>
+          <t>Partial Coverage</t>
         </is>
       </c>
       <c r="F25" s="63" t="n"/>
       <c r="G25" s="63" t="n"/>
       <c r="H25" s="63" t="n"/>
-      <c r="I25" s="63" t="n"/>
+      <c r="I25" s="97" t="inlineStr">
+        <is>
+          <t>Setup 2, Prompted Update Scenario 1 (optional CommCare APK prompt), and Prompted Update Scenario 2 (forced CommCare APK blocker, currently failing on-device - open investigation) are automated via scripts/run_suite.py + hq_setup/updates_2_49/*.json, with apk_version resolved dynamically against whichever HQ option is labeled "(dev)" (never hardcoded). Auto CC Update 1/3 and Rate Limit 1 are also automated. In-App Update 1-10 (real Play Store) and Scenario 3 (timed manual wait) remain not automatable.</t>
+        </is>
+      </c>
       <c r="J25" s="95" t="inlineStr">
         <is>
           <t>Partial Coverage (9/24)</t>

--- a/docs/Connect Test Case and Workflow Inventory.xlsx
+++ b/docs/Connect Test Case and Workflow Inventory.xlsx
@@ -7153,7 +7153,7 @@
       <c r="H22" s="63" t="n"/>
       <c r="I22" s="77" t="inlineStr">
         <is>
-          <t>SyncRecoveryTest (recovery sync) and AsyncRestoreTest (restore on login/sync) cover data-recovery paths, but the tab's forced app-update/reinstall recovery flows are not automated.</t>
+          <t>SyncRecoveryTest (recovery sync) and AsyncRestoreTest (restore on login/sync) cover data-recovery paths. UPDATE (2026-08-26): the tab's forced app-update/reinstall recovery flows ARE NOW automated - a new Appium-based module (scripts/appium_offline_ccz_scenarios.py + scripts/run_appium_offline_ccz_suite.py) pushes a real .ccz file onto the device via BrowserStack push_file (Maestro itself has no file-push mechanism), confirmed passing live in CI (run 32936440687). The CC Reinstall/Update Needed client-swap limitation is also resolved (whole-session-on-old-client dispatch, not a mid-session swap). See docs/[Master] Mobile Plan (2026).xlsx Recovery Measures tab for the row-level detail.</t>
         </is>
       </c>
       <c r="J22" s="95" t="inlineStr">

--- a/docs/Connect Test Case and Workflow Inventory.xlsx
+++ b/docs/Connect Test Case and Workflow Inventory.xlsx
@@ -7153,7 +7153,7 @@
       <c r="H22" s="63" t="n"/>
       <c r="I22" s="77" t="inlineStr">
         <is>
-          <t>SyncRecoveryTest (recovery sync) and AsyncRestoreTest (restore on login/sync) cover data-recovery paths. UPDATE (2026-08-26): the tab's forced app-update/reinstall recovery flows ARE NOW automated - a new Appium-based module (scripts/appium_offline_ccz_scenarios.py + scripts/run_appium_offline_ccz_suite.py) pushes a real .ccz file onto the device via BrowserStack push_file (Maestro itself has no file-push mechanism), confirmed passing live in CI (run 32936440687). The CC Reinstall/Update Needed client-swap limitation is also resolved (whole-session-on-old-client dispatch, not a mid-session swap). See docs/[Master] Mobile Plan (2026).xlsx Recovery Measures tab for the row-level detail.</t>
+          <t>SyncRecoveryTest (recovery sync) and AsyncRestoreTest (restore on login/sync) cover data-recovery paths. UPDATE (2026-08-26): the tab's forced app-update/reinstall recovery flows ARE NOW automated - a new Appium-based module (scripts/appium_offline_ccz_scenarios.py + scripts/run_appium_offline_ccz_suite.py) pushes a real .ccz file onto the device via BrowserStack push_file (Maestro itself has no file-push mechanism), confirmed passing live in CI (run 32936440687). The CC Reinstall/Update Needed client-swap limitation is also resolved (whole-session-on-old-client dispatch, not a mid-session swap). One exception: Retry Recovery 2 (network-toggle retry-button test) is Not Automatable - its measure is version-gated to CommCare client 2.45-2.54 only (confirmed via the app's own Django admin record), so it can't fire against the current release client under test regardless of automation approach. See docs/[Master] Mobile Plan (2026).xlsx Recovery Measures tab for the row-level detail.</t>
         </is>
       </c>
       <c r="J22" s="95" t="inlineStr">

--- a/docs/Connect Test Case and Workflow Inventory.xlsx
+++ b/docs/Connect Test Case and Workflow Inventory.xlsx
@@ -7,6 +7,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Connect Web" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Connect Mobile" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CommCare Mobile" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CommCare Mobile - Non-Core" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -384,7 +385,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -652,6 +653,10 @@
     </xf>
     <xf numFmtId="0" fontId="37" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -7330,4 +7335,534 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12.71" customWidth="1" style="86" min="1" max="1"/>
+    <col width="32" customWidth="1" style="86" min="2" max="2"/>
+    <col width="14" customWidth="1" style="86" min="3" max="3"/>
+    <col width="12" customWidth="1" style="86" min="4" max="4"/>
+    <col width="14" customWidth="1" style="86" min="5" max="5"/>
+    <col width="22" customWidth="1" style="86" min="6" max="6"/>
+    <col width="12" customWidth="1" style="86" min="7" max="7"/>
+    <col width="24" customWidth="1" style="86" min="8" max="8"/>
+    <col width="37.29" customWidth="1" style="86" min="9" max="9"/>
+    <col width="26" customWidth="1" style="86" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="91" t="inlineStr">
+        <is>
+          <t>Workflow Inventory – CommCare Mobile - Non-Core  |  Framework: N/A (outside Maestro automation program)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="130" customHeight="1" s="86">
+      <c r="A2" s="93" t="inlineStr">
+        <is>
+          <t>1. [Master] Mobile Plan (2026) - 15 sheets not yet listed in the "CommCare Mobile" tab above
+2. Existing Unit Tests coverage
+These 15 tabs predate/sit outside the Maestro automation program - confirmed 2026-09-01 that none of them even carry a "Maestro Automatability" column in the Master Plan (unlike every tab in the "CommCare Mobile" sheet above). Reviewed here for the first time against this program's actual proven capabilities (HQClient's mark_build_status/create_new_build/set_custom_properties/get_custom_properties/list_releases/get_app_install_code/find_recent_submission+get_form_metadata/edit_module_attr/check_for_phone_triggered_build; Appium's push_file/current_package/mid-session same-cert app install; confirmed dead ends: camera-image-injection, airplane-mode/network toggling on BrowserStack's real-device cloud, arbitrary third-party Play Store app installs with no internal APK source, device-clock manipulation, biometric hardware enrollment, real SMS OTP delivery, terminateApp/backgroundApp/pressKeyCode/adb_shell).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="69.75" customHeight="1" s="86">
+      <c r="A4" s="94" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="B4" s="94" t="inlineStr">
+        <is>
+          <t>Workflow Name</t>
+        </is>
+      </c>
+      <c r="C4" s="94" t="inlineStr">
+        <is>
+          <t>Release Type
+(every release / regression / ad-hoc)</t>
+        </is>
+      </c>
+      <c r="D4" s="94" t="inlineStr">
+        <is>
+          <t>Release Risk
+(High / Medium / Low)</t>
+        </is>
+      </c>
+      <c r="E4" s="94" t="inlineStr">
+        <is>
+          <t>Existing Script?
+(yes / no)</t>
+        </is>
+      </c>
+      <c r="F4" s="94" t="inlineStr">
+        <is>
+          <t>Existing Script Name
+(if yes)</t>
+        </is>
+      </c>
+      <c r="G4" s="94" t="inlineStr">
+        <is>
+          <t>Flakiness
+(High / Medium / Low / N/A)</t>
+        </is>
+      </c>
+      <c r="H4" s="94" t="inlineStr">
+        <is>
+          <t>Automation Action</t>
+        </is>
+      </c>
+      <c r="I4" s="94" t="inlineStr">
+        <is>
+          <t>Notes / Dependencies
+(CommCare dev needed? blocker? volatile?)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="90" customHeight="1" s="86">
+      <c r="A5" s="98" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="99" t="inlineStr">
+        <is>
+          <t>Database Change</t>
+        </is>
+      </c>
+      <c r="C5" s="98" t="n"/>
+      <c r="D5" s="98" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E5" s="98" t="inlineStr">
+        <is>
+          <t>Partial Coverage</t>
+        </is>
+      </c>
+      <c r="F5" s="98" t="n"/>
+      <c r="G5" s="98" t="n"/>
+      <c r="H5" s="98" t="n"/>
+      <c r="I5" s="99" t="inlineStr">
+        <is>
+          <t>Tests local DB survives a CommCare/app-build upgrade (incl. large version jumps), with outstanding saved/incomplete/case/multimedia data preserved and submittable after update. Setup 2-4 and Database 1-6 (offline form creation, standard Maestro) and Final 3-4 (disable airplane mode, sync, verify via HQClient.find_recent_submission) are automatable now. The version-jump rows don't need real Play Store access either - install_mid_session can push the target GitHub-release APK directly (same signing cert). Database Change Logs (10-12) are plain text assertions. Row 13 (Share via Gmail) - handoff confirmable via driver.current_package, actual email delivery/contents out of scope. No instrumentation-test overlap (SyncRecoveryTest.kt covers mid-sync recovery within one app version, not cross-version DB migration).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="90" customHeight="1" s="86">
+      <c r="A6" s="98" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="99" t="inlineStr">
+        <is>
+          <t>SD Card Dump</t>
+        </is>
+      </c>
+      <c r="C6" s="98" t="n"/>
+      <c r="D6" s="98" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E6" s="98" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F6" s="98" t="n"/>
+      <c r="G6" s="98" t="n"/>
+      <c r="H6" s="98" t="n"/>
+      <c r="I6" s="99" t="inlineStr">
+        <is>
+          <t>Not automatable, out of scope: requires TWO physical Android phones, each with a real SD card slot, plus physically removing/inserting an SD card between them to transfer forms. BrowserStack App Automate is single-real-device-per-session with no way to move physical removable media. No instrumentation overlap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="90" customHeight="1" s="86">
+      <c r="A7" s="98" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="99" t="inlineStr">
+        <is>
+          <t>Wi-Fi Direct</t>
+        </is>
+      </c>
+      <c r="C7" s="98" t="n"/>
+      <c r="D7" s="98" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E7" s="98" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F7" s="98" t="n"/>
+      <c r="G7" s="98" t="n"/>
+      <c r="H7" s="98" t="n"/>
+      <c r="I7" s="99" t="inlineStr">
+        <is>
+          <t>Not automatable, out of scope: requires two physical devices to peer-connect via Wi-Fi Direct and transfer forms device-to-device - inherently a two-real-device session a single-device cloud service cannot provide. No instrumentation overlap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="90" customHeight="1" s="86">
+      <c r="A8" s="98" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="99" t="inlineStr">
+        <is>
+          <t>Developer Options</t>
+        </is>
+      </c>
+      <c r="C8" s="98" t="n"/>
+      <c r="D8" s="98" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E8" s="98" t="inlineStr">
+        <is>
+          <t>Partial Coverage</t>
+        </is>
+      </c>
+      <c r="F8" s="98" t="n"/>
+      <c r="G8" s="98" t="n"/>
+      <c r="H8" s="98" t="n"/>
+      <c r="I8" s="99" t="inlineStr">
+        <is>
+          <t>Fully automatable in principle (single device, standard taps/asserts, no HQ/multi-device dependency) - and largely ALREADY covered, just not in this repo: commcare-android's DeveloperOptionsTests.kt (instrumentation) already exercises enabling Developer Mode and all 4 settings items (DO1), the Show Update Options toggle (DO2), and Image Above/Below Question Text with real Espresso isAbove/isBelow layout assertions (DO3/DO4) almost verbatim against this same sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="90" customHeight="1" s="86">
+      <c r="A9" s="98" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="99" t="inlineStr">
+        <is>
+          <t>Printing</t>
+        </is>
+      </c>
+      <c r="C9" s="98" t="n"/>
+      <c r="D9" s="98" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E9" s="98" t="inlineStr">
+        <is>
+          <t>Partial Coverage</t>
+        </is>
+      </c>
+      <c r="F9" s="98" t="n"/>
+      <c r="G9" s="98" t="n"/>
+      <c r="H9" s="98" t="n"/>
+      <c r="I9" s="99" t="inlineStr">
+        <is>
+          <t>Install/navigate/select-case steps are ordinary Maestro navigation. PDF generation (native Android print spooler UI) and verifying entered values appear correctly in the downloaded PDF are out of scope for a real tooling reason (not hardware): no file-content/PDF-rendering verification path exists in this repo's toolset, and the print spooler UI is largely outside Espresso/Maestro's reach. Instrumentation overlap is tangential only (AppPreferenceSettingsTest.kt's Set Print Template test picks a template FILE, not this sheet's PDF-output verification).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="90" customHeight="1" s="86">
+      <c r="A10" s="98" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="99" t="inlineStr">
+        <is>
+          <t>Graphing</t>
+        </is>
+      </c>
+      <c r="C10" s="98" t="n"/>
+      <c r="D10" s="98" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E10" s="98" t="inlineStr">
+        <is>
+          <t>Partial Coverage</t>
+        </is>
+      </c>
+      <c r="F10" s="98" t="n"/>
+      <c r="G10" s="98" t="n"/>
+      <c r="H10" s="98" t="n"/>
+      <c r="I10" s="99" t="inlineStr">
+        <is>
+          <t>Install/login/create-case/add-points navigation (Graphing 1-5) is plain Maestro. The real assertions (exact axis tick values, bar/bubble colors, zoom/pan/rotation not distorting) are out of scope for a genuine tooling reason: pixel/visual-rendering checks on a custom-drawn canvas, not accessibility-tree text Maestro can assert. No instrumentation overlap (TilesTest.kt tests an unrelated case-list UI).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="90" customHeight="1" s="86">
+      <c r="A11" s="98" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="99" t="inlineStr">
+        <is>
+          <t>NFC</t>
+        </is>
+      </c>
+      <c r="C11" s="98" t="n"/>
+      <c r="D11" s="98" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E11" s="98" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F11" s="98" t="n"/>
+      <c r="G11" s="98" t="n"/>
+      <c r="H11" s="98" t="n"/>
+      <c r="I11" s="99" t="inlineStr">
+        <is>
+          <t>Not automatable, out of scope - the sheet's own header states this can only be run on a specific NFC-capable tablet physically located at a specific Dimagi office, tapped against a physical NFC bracelet. No BrowserStack cloud device offers this. No instrumentation overlap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="90" customHeight="1" s="86">
+      <c r="A12" s="98" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="99" t="inlineStr">
+        <is>
+          <t>Auto Form Submission</t>
+        </is>
+      </c>
+      <c r="C12" s="98" t="n"/>
+      <c r="D12" s="98" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E12" s="98" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F12" s="98" t="n"/>
+      <c r="G12" s="98" t="n"/>
+      <c r="H12" s="98" t="n"/>
+      <c r="I12" s="99" t="inlineStr">
+        <is>
+          <t>Not automatable, out of scope: relies on airplane-mode/network toggling (confirmed unreliable on BrowserStack's real-device cloud this session) AND simulating a specific low-battery device state, neither of which this stack can do. No instrumentation overlap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="90" customHeight="1" s="86">
+      <c r="A13" s="98" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="99" t="inlineStr">
+        <is>
+          <t>Mapbox</t>
+        </is>
+      </c>
+      <c r="C13" s="98" t="n"/>
+      <c r="D13" s="98" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E13" s="98" t="inlineStr">
+        <is>
+          <t>Partial Coverage</t>
+        </is>
+      </c>
+      <c r="F13" s="98" t="n"/>
+      <c r="G13" s="98" t="n"/>
+      <c r="H13" s="98" t="n"/>
+      <c r="I13" s="99" t="inlineStr">
+        <is>
+          <t>Mapbox 1, 2, 5 (map-style rendering, case-list geopoint display) are standard Maestro taps/asserts on real UI elements. Mapbox 3-4 (disable device GPS / deny location permission via the real Android Settings app) are plausibly reachable via ordinary taps but unproven in this repo - flag as lower-confidence, not assumed reliable, until tried live. No instrumentation overlap (no GPS/location logic in the 35 files).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="90" customHeight="1" s="86">
+      <c r="A14" s="98" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="99" t="inlineStr">
+        <is>
+          <t>Text to Speech</t>
+        </is>
+      </c>
+      <c r="C14" s="98" t="n"/>
+      <c r="D14" s="98" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E14" s="98" t="inlineStr">
+        <is>
+          <t>Partial Coverage</t>
+        </is>
+      </c>
+      <c r="F14" s="98" t="n"/>
+      <c r="G14" s="98" t="n"/>
+      <c r="H14" s="98" t="n"/>
+      <c r="I14" s="99" t="inlineStr">
+        <is>
+          <t>TTS 1-4 (enable setting, audio-button presence, language-switch persistence) are standard taps/asserts. TTS 5-6 (delete/add on-device Google TTS language packs via native OEM TTS engine settings) vary across BrowserStack's device pool - not reliably automatable, skip. LanguagesTest.kt covers app-language-change persistence generically but has no TTS/audio-button assertions - tangential, not real coverage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="90" customHeight="1" s="86">
+      <c r="A15" s="98" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="99" t="inlineStr">
+        <is>
+          <t>Third Party Scanner</t>
+        </is>
+      </c>
+      <c r="C15" s="98" t="n"/>
+      <c r="D15" s="98" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E15" s="98" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F15" s="98" t="n"/>
+      <c r="G15" s="98" t="n"/>
+      <c r="H15" s="98" t="n"/>
+      <c r="I15" s="99" t="inlineStr">
+        <is>
+          <t>Not automatable, out of scope: the entire premise (row 1: "Open Play Store, download QR Droid") requires installing an arbitrary third-party Play Store app with no internal APK source - a confirmed hard limit of this pipeline (same class of gap as Other-Error Tests' Callout Setup/Arbitrary Intent rows). No instrumentation overlap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="90" customHeight="1" s="86">
+      <c r="A16" s="98" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="99" t="inlineStr">
+        <is>
+          <t>Advanced Settings</t>
+        </is>
+      </c>
+      <c r="C16" s="98" t="n"/>
+      <c r="D16" s="98" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E16" s="98" t="inlineStr">
+        <is>
+          <t>Partial Coverage</t>
+        </is>
+      </c>
+      <c r="F16" s="98" t="n"/>
+      <c r="G16" s="98" t="n"/>
+      <c r="H16" s="98" t="n"/>
+      <c r="I16" s="99" t="inlineStr">
+        <is>
+          <t>Strongly automatable: most Custom Properties rows (1,2,4-9,11-16) map directly onto the proven HQClient.set_custom_properties/get_custom_properties mechanism plus a standard on-device assertion of the resulting UI. Settings 1/3/4 are plain UI assertions. Custom Properties 3 (device-clock change) and Settings 2 (device-date change) are blocked - real device-clock manipulation is a confirmed hard limit. Real instrumentation overlap: DeveloperOptionsTests.kt exercises the exact cc-superuser-enabled -&gt; Developer Options flow (Custom Properties 4); MediaEncryptionTest.kt directly toggles HiddenPreferences.ENCRYPT_CAPTURED_MEDIA, matching cc-encrypt-captured-media (Custom Properties 16).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="90" customHeight="1" s="86">
+      <c r="A17" s="98" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="99" t="inlineStr">
+        <is>
+          <t>Performance Tests</t>
+        </is>
+      </c>
+      <c r="C17" s="98" t="n"/>
+      <c r="D17" s="98" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E17" s="98" t="inlineStr">
+        <is>
+          <t>Partial Coverage</t>
+        </is>
+      </c>
+      <c r="F17" s="98" t="n"/>
+      <c r="G17" s="98" t="n"/>
+      <c r="H17" s="98" t="n"/>
+      <c r="I17" s="99" t="inlineStr">
+        <is>
+          <t>Install-old-APK-then-update matches the proven mid-session app-install pattern (AppiumBrowserStackClient.install_mid_session, same-signing-cert APKs, already used for update scenarios). "Time taken" rows are measurable via code-level timestamps around driver actions instead of a human stopwatch - no fundamental hardware blocker. No instrumentation overlap (no timing/perf measurement in the 35 files).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="90" customHeight="1" s="86">
+      <c r="A18" s="98" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="99" t="inlineStr">
+        <is>
+          <t>Case List Optimization and Cach</t>
+        </is>
+      </c>
+      <c r="C18" s="98" t="n"/>
+      <c r="D18" s="98" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E18" s="98" t="inlineStr">
+        <is>
+          <t>Partial Coverage</t>
+        </is>
+      </c>
+      <c r="F18" s="98" t="n"/>
+      <c r="G18" s="98" t="n"/>
+      <c r="H18" s="98" t="n"/>
+      <c r="I18" s="99" t="inlineStr">
+        <is>
+          <t>Setup/Cache-and-index/Load-time rows are automatable via timestamped navigation (same technique as Performance Tests above). Load-time-6 (clear app data) and -7 (force-stop) are blocked: terminateApp/pressKeyCode are confirmed unsupported via Appium on BrowserStack, and its managed Appium server has adb_shell disabled - no way to force-stop or clear data. The Exploratory-testing row is inherently manual. Instrumentation overlap is weak (CaseListSortTest.kt/CaseListSearchTest.kt test sort/search correctness on a different app, not this sheet's cache/lazy-load performance settings).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="90" customHeight="1" s="86">
+      <c r="A19" s="98" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="99" t="inlineStr">
+        <is>
+          <t>Personal ID</t>
+        </is>
+      </c>
+      <c r="C19" s="98" t="n"/>
+      <c r="D19" s="98" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E19" s="98" t="inlineStr">
+        <is>
+          <t>No - wrong product for most rows</t>
+        </is>
+      </c>
+      <c r="F19" s="98" t="n"/>
+      <c r="G19" s="98" t="n"/>
+      <c r="H19" s="98" t="n"/>
+      <c r="I19" s="99" t="inlineStr">
+        <is>
+          <t>Mostly does not belong in a CommCare Mobile inventory: TC_05-36 are Dimagi Connect/PersonalID's own onboarding UI (phone OTP verification, Android biometric enrollment, backup codes, selfie capture) - a different product surface. Only TC_01-04 (existing-user sign-in/update continuity) and TC_37-47 (MW-to-PersonalID link/unlink popups inside CommCare, HQ mobile-workers-page column) genuinely touch CommCare Mobile, and even those are doubly blocked where they depend on real SMS OTP delivery or biometric hardware enrollment - two more confirmed hard limits. No instrumentation overlap.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/Connect Test Case and Workflow Inventory.xlsx
+++ b/docs/Connect Test Case and Workflow Inventory.xlsx
@@ -6571,14 +6571,14 @@
       </c>
       <c r="J6" s="95" t="inlineStr">
         <is>
-          <t>Partial Coverage (6/7)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K6" s="0" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L6" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" ht="45.75" customHeight="1" s="86">
@@ -6647,14 +6647,14 @@
       </c>
       <c r="J8" s="95" t="inlineStr">
         <is>
-          <t>Partial Coverage (7/14)</t>
+          <t>Partial Coverage (9/14)</t>
         </is>
       </c>
       <c r="K8" s="0" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L8" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" ht="45.75" customHeight="1" s="86">
@@ -6723,14 +6723,14 @@
       </c>
       <c r="J10" s="95" t="inlineStr">
         <is>
-          <t>Partial Coverage (48/66)</t>
+          <t>Partial Coverage (50/66)</t>
         </is>
       </c>
       <c r="K10" s="0" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L10" s="0" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" ht="45.75" customHeight="1" s="86">
@@ -7123,14 +7123,14 @@
       <c r="I21" s="63" t="n"/>
       <c r="J21" s="95" t="inlineStr">
         <is>
-          <t>Partial Coverage (24/30)</t>
+          <t>Partial Coverage (26/28)</t>
         </is>
       </c>
       <c r="K21" s="0" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="L21" s="0" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" ht="57" customHeight="1" s="86">
@@ -7163,14 +7163,14 @@
       </c>
       <c r="J22" s="95" t="inlineStr">
         <is>
-          <t>Partial Coverage (44/47)</t>
+          <t>Partial Coverage (43/47)</t>
         </is>
       </c>
       <c r="K22" s="0" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L22" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23" ht="39.75" customHeight="1" s="86">
@@ -7199,14 +7199,14 @@
       <c r="I23" s="63" t="n"/>
       <c r="J23" s="95" t="inlineStr">
         <is>
-          <t>Partial Coverage (29/51)</t>
+          <t>Partial Coverage (30/51)</t>
         </is>
       </c>
       <c r="K23" s="0" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L23" s="0" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24" ht="44.25" customHeight="1" s="86">
@@ -7239,14 +7239,14 @@
       </c>
       <c r="J24" s="95" t="inlineStr">
         <is>
-          <t>Partial Coverage (1/4)</t>
+          <t>Partial Coverage (3/4)</t>
         </is>
       </c>
       <c r="K24" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="L24" s="0" t="n">
         <v>1</v>
-      </c>
-      <c r="L24" s="0" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="25" ht="14.25" customHeight="1" s="86">
@@ -7279,14 +7279,14 @@
       </c>
       <c r="J25" s="95" t="inlineStr">
         <is>
-          <t>Partial Coverage (9/24)</t>
+          <t>Partial Coverage (10/24)</t>
         </is>
       </c>
       <c r="K25" s="0" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L25" s="0" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="27">
@@ -7296,14 +7296,14 @@
         </is>
       </c>
       <c r="K27" s="0" t="n">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="L27" s="0" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="M27" s="0" t="inlineStr">
         <is>
-          <t>63.1% automated (250/396 test cases)</t>
+          <t>66.2% automated (260/393 test cases)</t>
         </is>
       </c>
     </row>

--- a/docs/Connect Test Case and Workflow Inventory.xlsx
+++ b/docs/Connect Test Case and Workflow Inventory.xlsx
@@ -7199,11 +7199,11 @@
       <c r="I23" s="63" t="n"/>
       <c r="J23" s="95" t="inlineStr">
         <is>
-          <t>Partial Coverage (30/51)</t>
+          <t>Partial Coverage (29/51)</t>
         </is>
       </c>
       <c r="K23" s="0" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L23" s="0" t="n">
         <v>20</v>
@@ -7296,14 +7296,14 @@
         </is>
       </c>
       <c r="K27" s="0" t="n">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="L27" s="0" t="n">
-        <v>133</v>
+        <v>98</v>
       </c>
       <c r="M27" s="0" t="inlineStr">
         <is>
-          <t>66.2% automated (260/393 test cases)</t>
+          <t>71.9% automated (259/360 test cases) - excludes Browserstack/Android Virtual Devices (35 test cases, already marked Not automatable/out of scope for Maestro)</t>
         </is>
       </c>
     </row>
